--- a/outputs/evaluation/architecture/design/v2/CF_M05/run_2/CF_M05_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/design/v2/CF_M05/run_2/CF_M05_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.3659</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.5263</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.4118</v>
       </c>
       <c r="D3" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9350000000000001</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.1429</v>
       </c>
       <c r="D4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8003</v>
       </c>
     </row>
@@ -1221,14 +1235,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Portal Microservice</t>
@@ -1255,13 +1266,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M05_AU02</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1302,14 +1311,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Leader Microservice</t>
@@ -1335,13 +1341,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M05_AU01</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1362,7 +1366,6 @@
       <c r="D4" t="n">
         <v>0.8003</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1383,7 +1386,6 @@
           <t>['AU_08', 'AU_09']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_11</t>
@@ -1394,7 +1396,6 @@
           <t>angular, spring boot</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1413,7 +1414,6 @@
           <t>CF_M05_AU14, CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M05_AU34</t>
@@ -1464,14 +1464,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Scheduler Microservice</t>
@@ -1500,13 +1497,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M05_AU05</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1547,14 +1542,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Communication Log Microservice</t>
@@ -1583,13 +1575,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M05_AU04</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1630,14 +1620,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Access Control Microservice</t>
@@ -1662,13 +1649,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M05_AU03</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1709,14 +1694,11 @@
           <t>68</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>P_05</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Layered Architecture</t>
@@ -1738,14 +1720,11 @@
       <c r="P8" t="n">
         <v>68.69</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1786,14 +1765,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Cloud Architecture</t>
@@ -1813,14 +1789,11 @@
       <c r="P9" t="n">
         <v>60</v>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M05_P05</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1861,14 +1834,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>GSB</t>
@@ -1893,13 +1863,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M05_AU12</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1940,14 +1908,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Ordering</t>
@@ -1974,13 +1939,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M05_AU11</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2021,14 +1984,11 @@
           <t>76</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Spring Boot</t>
@@ -2054,13 +2014,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M05_AU29</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2101,14 +2059,11 @@
           <t>62</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>MVVM</t>
@@ -2128,14 +2083,11 @@
       <c r="P13" t="n">
         <v>62</v>
       </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2176,14 +2128,11 @@
           <t>76</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Angular</t>
@@ -2207,13 +2156,11 @@
           <t>CF_M05_AU06</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M05_AU30</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2254,14 +2201,11 @@
           <t>9, 56</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Microservices</t>
@@ -2280,14 +2224,11 @@
       <c r="P15" t="n">
         <v>56</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2328,14 +2269,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -2356,7 +2294,6 @@
       <c r="P16" t="n">
         <v>61</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Design Pattern</t>
@@ -2367,7 +2304,6 @@
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2441,7 +2377,6 @@
           <t>Amazon Web Services</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>The provider for this project is Amazon Web Services which has a wide catalog of cloud services and resources.</t>
@@ -2533,7 +2468,6 @@
           <t>Client(Frontend)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>The client, also called the frontEnd, is responsible for the presentation and user experience
@@ -2571,7 +2505,6 @@
           <t>Amazon EKS</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">For the deployment of the application, Amazon EKS has been used, a service offered by AWS
@@ -2609,7 +2542,6 @@
           <t>SonarQube</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>SonarQube is a
@@ -2648,7 +2580,6 @@
           <t>Grafana</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
@@ -2684,7 +2615,6 @@
           <t>Amazon RDS</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
@@ -2721,7 +2651,6 @@
           <t>View</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>The component we call View, Vista in Catalan, is made up of the HTML and SCSS files of
@@ -2759,7 +2688,6 @@
           <t>ViewModel</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>The ViewModel component groups the TS files of the components and the services they
@@ -2797,7 +2725,6 @@
           <t>Model</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Models are the TypeScript classes that define the data contract consumed by the
@@ -2835,7 +2762,6 @@
           <t>Database</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
@@ -2873,7 +2799,6 @@
           <t>Presentation Layer (Controllers)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>The controllers, through specific
@@ -2911,7 +2836,6 @@
           <t>Business Logic Layer (Services)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Services provide the interface and implementation of all the application's business logic.</t>
@@ -2947,7 +2871,6 @@
           <t>Domain Layer (Models)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Models represent the internal and persistent structure of the system entities, reflecting the
@@ -2984,7 +2907,6 @@
           <t>Contract Layer (DTO/Mappers)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
@@ -3021,7 +2943,6 @@
           <t>Data access layer (Repositories)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>the Repositories are responsible for performing queries on the database.</t>
@@ -3052,7 +2973,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, ordering, gsb</t>
@@ -3088,7 +3008,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>communication log microservice, leader microservice, portal microservice, access control microservice, scheduler microservice, client(frontend), amazon eks</t>
@@ -3124,7 +3043,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>client(frontend), server (backend)</t>
@@ -3160,7 +3078,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>presentation layer (controllers), data access layer (repositories)</t>
@@ -3176,7 +3093,6 @@
           <t>AU_11</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>0.7131999999999999</v>
       </c>
@@ -3192,7 +3108,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>data access layer (repositories), database</t>
@@ -3208,7 +3123,6 @@
           <t>AU_11</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>0.666</v>
       </c>
@@ -3224,7 +3138,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>viewmodel, view, model</t>
@@ -3265,7 +3178,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
@@ -3302,7 +3214,6 @@
           <t>HTTP</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>The message
@@ -3314,7 +3225,6 @@
           <t>AU_11</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>0.8887</v>
       </c>
@@ -3335,7 +3245,6 @@
           <t>Server (Backend)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
@@ -3372,7 +3281,6 @@
           <t>Docker</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>The deployment process for our application begins with the creation of a Docker image [28] for each microservice which has its own repository with a Dockerfile [29].</t>
@@ -3408,7 +3316,6 @@
           <t>Kubernetes</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>which allows the use of Kubernetes (K8s), a container orchestration platform created by
@@ -3445,7 +3352,6 @@
           <t>Shared Database</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
